--- a/BOM锁定表-V2.2.xlsx
+++ b/BOM锁定表-V2.2.xlsx
@@ -434,7 +434,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -711,7 +711,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>¥18–28（估算，须向佳显正式询价）</t>
+          <t>¥9.00（V2.2 需求方给定假设） ⚠️ 须确认是黑白双色还是红黑白三色（FPC 针数可能不同，且影响固件是否用红色）</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/BOM锁定表-V2.2.xlsx
+++ b/BOM锁定表-V2.2.xlsx
@@ -434,7 +434,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
